--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AE606B-BAA0-4119-84AD-3459B2BB9F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6904FD8-B353-43BA-98AA-BD92AF2D3F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12225" yWindow="2625" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -738,12 +738,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1520,6 +1519,9 @@
       <c r="C30">
         <v>2023</v>
       </c>
+      <c r="D30">
+        <v>2026</v>
+      </c>
       <c r="M30" s="3">
         <v>10</v>
       </c>
@@ -1534,6 +1536,9 @@
       <c r="C31">
         <v>28</v>
       </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="P31" s="3"/>
@@ -1544,6 +1549,9 @@
       <c r="C32">
         <v>28</v>
       </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="P32" s="3"/>
@@ -1554,6 +1562,9 @@
       <c r="C33">
         <v>10</v>
       </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="P33" s="3"/>
@@ -1623,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="N38" s="3"/>
-      <c r="P38" s="4" t="s">
+      <c r="P38" s="3" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1638,7 +1649,7 @@
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="P39" s="4"/>
+      <c r="P39" s="3"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
@@ -1651,7 +1662,7 @@
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="P40" s="4"/>
+      <c r="P40" s="3"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
@@ -1664,7 +1675,7 @@
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-      <c r="P41" s="4"/>
+      <c r="P41" s="3"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
@@ -1683,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="N42" s="3"/>
-      <c r="P42" s="4" t="s">
+      <c r="P42" s="3" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1698,7 +1709,7 @@
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="P43" s="4"/>
+      <c r="P43" s="3"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
@@ -1711,7 +1722,7 @@
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
-      <c r="P44" s="4"/>
+      <c r="P44" s="3"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
@@ -1724,7 +1735,7 @@
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
-      <c r="P45" s="4"/>
+      <c r="P45" s="3"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -1740,7 +1751,7 @@
         <v>10</v>
       </c>
       <c r="N46" s="3"/>
-      <c r="P46" s="4" t="s">
+      <c r="P46" s="3" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1752,7 +1763,7 @@
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="P47" s="4"/>
+      <c r="P47" s="3"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
@@ -1762,7 +1773,7 @@
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
-      <c r="P48" s="4"/>
+      <c r="P48" s="3"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
@@ -1772,7 +1783,7 @@
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
-      <c r="P49" s="4"/>
+      <c r="P49" s="3"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
@@ -1788,7 +1799,7 @@
         <v>9</v>
       </c>
       <c r="N50" s="3"/>
-      <c r="P50" s="4" t="s">
+      <c r="P50" s="3" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1800,7 +1811,7 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
-      <c r="P51" s="4"/>
+      <c r="P51" s="3"/>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
@@ -1810,7 +1821,7 @@
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-      <c r="P52" s="4"/>
+      <c r="P52" s="3"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -1820,7 +1831,7 @@
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
-      <c r="P53" s="4"/>
+      <c r="P53" s="3"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
@@ -1836,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="N54" s="3"/>
-      <c r="P54" s="4" t="s">
+      <c r="P54" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1848,7 +1859,7 @@
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="P55" s="4"/>
+      <c r="P55" s="3"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
@@ -1858,7 +1869,7 @@
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-      <c r="P56" s="4"/>
+      <c r="P56" s="3"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
@@ -1868,7 +1879,7 @@
       </c>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-      <c r="P57" s="4"/>
+      <c r="P57" s="3"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
@@ -1884,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="N58" s="3"/>
-      <c r="P58" s="4" t="s">
+      <c r="P58" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1896,7 +1907,7 @@
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
-      <c r="P59" s="4"/>
+      <c r="P59" s="3"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
@@ -1906,7 +1917,7 @@
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="P60" s="4"/>
+      <c r="P60" s="3"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -1916,7 +1927,7 @@
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
-      <c r="P61" s="4"/>
+      <c r="P61" s="3"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
@@ -1938,7 +1949,7 @@
         <v>10</v>
       </c>
       <c r="N62" s="3"/>
-      <c r="P62" s="4" t="s">
+      <c r="P62" s="3" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1956,7 +1967,7 @@
       </c>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-      <c r="P63" s="4"/>
+      <c r="P63" s="3"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
@@ -1972,7 +1983,7 @@
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-      <c r="P64" s="4"/>
+      <c r="P64" s="3"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
@@ -1988,7 +1999,7 @@
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
-      <c r="P65" s="4"/>
+      <c r="P65" s="3"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
@@ -2004,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="N66" s="3"/>
-      <c r="P66" s="4" t="s">
+      <c r="P66" s="3" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2016,7 +2027,7 @@
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-      <c r="P67" s="4"/>
+      <c r="P67" s="3"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
@@ -2026,7 +2037,7 @@
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="P68" s="4"/>
+      <c r="P68" s="3"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
@@ -2036,7 +2047,7 @@
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
-      <c r="P69" s="4"/>
+      <c r="P69" s="3"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
@@ -2052,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="N70" s="3"/>
-      <c r="P70" s="4" t="s">
+      <c r="P70" s="3" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2064,7 +2075,7 @@
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="P71" s="4"/>
+      <c r="P71" s="3"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
@@ -2074,7 +2085,7 @@
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
-      <c r="P72" s="4"/>
+      <c r="P72" s="3"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
@@ -2084,7 +2095,7 @@
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="P73" s="4"/>
+      <c r="P73" s="3"/>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
@@ -2100,7 +2111,7 @@
         <v>8.5</v>
       </c>
       <c r="N74" s="3"/>
-      <c r="P74" s="4" t="s">
+      <c r="P74" s="3" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2112,7 +2123,7 @@
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-      <c r="P75" s="4"/>
+      <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
@@ -2122,7 +2133,7 @@
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
-      <c r="P76" s="4"/>
+      <c r="P76" s="3"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
@@ -2132,7 +2143,7 @@
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
-      <c r="P77" s="4"/>
+      <c r="P77" s="3"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
@@ -2151,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="N78" s="3"/>
-      <c r="P78" s="4" t="s">
+      <c r="P78" s="3" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2166,7 +2177,7 @@
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
-      <c r="P79" s="4"/>
+      <c r="P79" s="3"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
@@ -2179,7 +2190,7 @@
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
-      <c r="P80" s="4"/>
+      <c r="P80" s="3"/>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
@@ -2189,7 +2200,7 @@
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
-      <c r="P81" s="4"/>
+      <c r="P81" s="3"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
@@ -2208,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="N82" s="3"/>
-      <c r="P82" s="4" t="s">
+      <c r="P82" s="3" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2223,7 +2234,7 @@
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="P83" s="4"/>
+      <c r="P83" s="3"/>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
@@ -2236,7 +2247,7 @@
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-      <c r="P84" s="4"/>
+      <c r="P84" s="3"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
@@ -2246,7 +2257,7 @@
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="P85" s="4"/>
+      <c r="P85" s="3"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
@@ -2265,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="N86" s="3"/>
-      <c r="P86" s="4" t="s">
+      <c r="P86" s="3" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2280,7 +2291,7 @@
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
-      <c r="P87" s="4"/>
+      <c r="P87" s="3"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
@@ -2293,7 +2304,7 @@
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-      <c r="P88" s="4"/>
+      <c r="P88" s="3"/>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
@@ -2303,7 +2314,7 @@
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
-      <c r="P89" s="4"/>
+      <c r="P89" s="3"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
@@ -2319,7 +2330,7 @@
         <v>8.5</v>
       </c>
       <c r="N90" s="3"/>
-      <c r="P90" s="4" t="s">
+      <c r="P90" s="3" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2331,7 +2342,7 @@
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
-      <c r="P91" s="4"/>
+      <c r="P91" s="3"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
@@ -2341,7 +2352,7 @@
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
-      <c r="P92" s="4"/>
+      <c r="P92" s="3"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
@@ -2351,7 +2362,7 @@
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
-      <c r="P93" s="4"/>
+      <c r="P93" s="3"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
@@ -2367,7 +2378,7 @@
         <v>9</v>
       </c>
       <c r="N94" s="3"/>
-      <c r="P94" s="4" t="s">
+      <c r="P94" s="3" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2379,7 +2390,7 @@
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-      <c r="P95" s="4"/>
+      <c r="P95" s="3"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
@@ -2389,7 +2400,7 @@
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
-      <c r="P96" s="4"/>
+      <c r="P96" s="3"/>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
@@ -2408,7 +2419,7 @@
       <c r="L97" s="1"/>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
-      <c r="P97" s="4"/>
+      <c r="P97" s="3"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
@@ -2473,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="N102" s="3"/>
-      <c r="P102" s="4" t="s">
+      <c r="P102" s="3" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2488,7 +2499,7 @@
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
-      <c r="P103" s="4"/>
+      <c r="P103" s="3"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
@@ -2501,7 +2512,7 @@
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
-      <c r="P104" s="4"/>
+      <c r="P104" s="3"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
@@ -2514,7 +2525,7 @@
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
-      <c r="P105" s="4"/>
+      <c r="P105" s="3"/>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
@@ -2854,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="N130" s="3"/>
-      <c r="P130" s="4" t="s">
+      <c r="P130" s="3" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2869,7 +2880,7 @@
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
-      <c r="P131" s="4"/>
+      <c r="P131" s="3"/>
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
@@ -2882,7 +2893,7 @@
       </c>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
-      <c r="P132" s="4"/>
+      <c r="P132" s="3"/>
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
@@ -2895,7 +2906,7 @@
       </c>
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
-      <c r="P133" s="4"/>
+      <c r="P133" s="3"/>
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
@@ -2914,7 +2925,7 @@
         <v>8</v>
       </c>
       <c r="N134" s="3"/>
-      <c r="P134" s="4" t="s">
+      <c r="P134" s="3" t="s">
         <v>154</v>
       </c>
       <c r="Q134" s="1"/>
@@ -2939,7 +2950,7 @@
       </c>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
-      <c r="P135" s="4"/>
+      <c r="P135" s="3"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
@@ -2962,7 +2973,7 @@
       </c>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
-      <c r="P136" s="4"/>
+      <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
@@ -2972,7 +2983,7 @@
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
-      <c r="P137" s="4"/>
+      <c r="P137" s="3"/>
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
@@ -3960,39 +3971,206 @@
     </row>
   </sheetData>
   <mergeCells count="257">
-    <mergeCell ref="N50:N53"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="M38:M41"/>
-    <mergeCell ref="N38:N41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="M42:M45"/>
-    <mergeCell ref="N42:N45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="M46:M49"/>
-    <mergeCell ref="N46:N49"/>
-    <mergeCell ref="O22:O25"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="M14:M17"/>
-    <mergeCell ref="O14:O17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="M18:M21"/>
-    <mergeCell ref="O18:O21"/>
-    <mergeCell ref="N2:N5"/>
-    <mergeCell ref="M6:M9"/>
-    <mergeCell ref="O6:O9"/>
-    <mergeCell ref="M10:M13"/>
-    <mergeCell ref="O10:O13"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="P182:P185"/>
+    <mergeCell ref="P186:P189"/>
+    <mergeCell ref="P190:P193"/>
+    <mergeCell ref="P194:P197"/>
+    <mergeCell ref="P146:P149"/>
+    <mergeCell ref="P150:P153"/>
+    <mergeCell ref="P154:P157"/>
+    <mergeCell ref="P158:P161"/>
+    <mergeCell ref="P162:P165"/>
+    <mergeCell ref="P166:P169"/>
+    <mergeCell ref="P170:P173"/>
+    <mergeCell ref="P174:P177"/>
+    <mergeCell ref="P178:P181"/>
+    <mergeCell ref="P110:P113"/>
+    <mergeCell ref="P114:P117"/>
+    <mergeCell ref="P118:P121"/>
+    <mergeCell ref="P122:P125"/>
+    <mergeCell ref="P126:P129"/>
+    <mergeCell ref="P130:P133"/>
+    <mergeCell ref="P134:P137"/>
+    <mergeCell ref="P138:P141"/>
+    <mergeCell ref="P142:P145"/>
+    <mergeCell ref="P74:P77"/>
+    <mergeCell ref="P78:P81"/>
+    <mergeCell ref="P82:P85"/>
+    <mergeCell ref="P86:P89"/>
+    <mergeCell ref="P90:P93"/>
+    <mergeCell ref="P94:P97"/>
+    <mergeCell ref="P98:P101"/>
+    <mergeCell ref="P102:P105"/>
+    <mergeCell ref="P106:P109"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="P42:P45"/>
+    <mergeCell ref="P46:P49"/>
+    <mergeCell ref="P50:P53"/>
+    <mergeCell ref="P54:P57"/>
+    <mergeCell ref="P58:P61"/>
+    <mergeCell ref="P62:P65"/>
+    <mergeCell ref="P66:P69"/>
+    <mergeCell ref="P70:P73"/>
+    <mergeCell ref="P2:P5"/>
+    <mergeCell ref="P6:P9"/>
+    <mergeCell ref="P10:P13"/>
+    <mergeCell ref="P14:P17"/>
+    <mergeCell ref="P18:P21"/>
+    <mergeCell ref="P22:P25"/>
+    <mergeCell ref="P26:P29"/>
+    <mergeCell ref="P30:P33"/>
+    <mergeCell ref="P34:P37"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="M202:M205"/>
+    <mergeCell ref="N202:N205"/>
+    <mergeCell ref="A206:A209"/>
+    <mergeCell ref="B206:B209"/>
+    <mergeCell ref="M206:M209"/>
+    <mergeCell ref="N206:N209"/>
+    <mergeCell ref="M198:M201"/>
+    <mergeCell ref="N198:N201"/>
+    <mergeCell ref="N162:N165"/>
+    <mergeCell ref="M166:M169"/>
+    <mergeCell ref="N166:N169"/>
+    <mergeCell ref="N146:N149"/>
+    <mergeCell ref="M150:M153"/>
+    <mergeCell ref="N150:N153"/>
+    <mergeCell ref="M154:M157"/>
+    <mergeCell ref="N154:N157"/>
+    <mergeCell ref="N194:N197"/>
+    <mergeCell ref="N182:N185"/>
+    <mergeCell ref="M186:M189"/>
+    <mergeCell ref="N186:N189"/>
+    <mergeCell ref="M190:M193"/>
+    <mergeCell ref="N190:N193"/>
+    <mergeCell ref="N170:N173"/>
+    <mergeCell ref="M174:M177"/>
+    <mergeCell ref="N174:N177"/>
+    <mergeCell ref="M178:M181"/>
+    <mergeCell ref="N178:N181"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="M122:M125"/>
+    <mergeCell ref="M134:M137"/>
+    <mergeCell ref="M146:M149"/>
+    <mergeCell ref="M158:M161"/>
+    <mergeCell ref="M170:M173"/>
+    <mergeCell ref="M182:M185"/>
+    <mergeCell ref="M194:M197"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="M114:M117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="M118:M121"/>
+    <mergeCell ref="N118:N121"/>
+    <mergeCell ref="N134:N137"/>
+    <mergeCell ref="M138:M141"/>
+    <mergeCell ref="N138:N141"/>
+    <mergeCell ref="M142:M145"/>
+    <mergeCell ref="N142:N145"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="M126:M129"/>
+    <mergeCell ref="N126:N129"/>
+    <mergeCell ref="M130:M133"/>
+    <mergeCell ref="N130:N133"/>
+    <mergeCell ref="N158:N161"/>
+    <mergeCell ref="M162:M165"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="M102:M105"/>
+    <mergeCell ref="M106:M109"/>
+    <mergeCell ref="M110:M113"/>
+    <mergeCell ref="N102:N105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="N106:N109"/>
+    <mergeCell ref="M90:M93"/>
+    <mergeCell ref="N90:N93"/>
+    <mergeCell ref="M94:M97"/>
+    <mergeCell ref="N94:N97"/>
+    <mergeCell ref="M98:M101"/>
+    <mergeCell ref="N98:N101"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="M62:M65"/>
+    <mergeCell ref="N62:N65"/>
+    <mergeCell ref="M66:M69"/>
+    <mergeCell ref="N66:N69"/>
+    <mergeCell ref="M70:M73"/>
+    <mergeCell ref="N70:N73"/>
+    <mergeCell ref="M74:M77"/>
+    <mergeCell ref="N74:N77"/>
+    <mergeCell ref="M78:M81"/>
+    <mergeCell ref="N78:N81"/>
+    <mergeCell ref="M82:M85"/>
+    <mergeCell ref="N82:N85"/>
+    <mergeCell ref="M86:M89"/>
+    <mergeCell ref="N86:N89"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="M54:M57"/>
     <mergeCell ref="N54:N57"/>
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="B58:B61"/>
@@ -4017,206 +4195,39 @@
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="M50:M53"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="M54:M57"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="M90:M93"/>
-    <mergeCell ref="N90:N93"/>
-    <mergeCell ref="M94:M97"/>
-    <mergeCell ref="N94:N97"/>
-    <mergeCell ref="M98:M101"/>
-    <mergeCell ref="N98:N101"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="M62:M65"/>
-    <mergeCell ref="N62:N65"/>
-    <mergeCell ref="M66:M69"/>
-    <mergeCell ref="N66:N69"/>
-    <mergeCell ref="M70:M73"/>
-    <mergeCell ref="N70:N73"/>
-    <mergeCell ref="M74:M77"/>
-    <mergeCell ref="N74:N77"/>
-    <mergeCell ref="M78:M81"/>
-    <mergeCell ref="N78:N81"/>
-    <mergeCell ref="M82:M85"/>
-    <mergeCell ref="N82:N85"/>
-    <mergeCell ref="M86:M89"/>
-    <mergeCell ref="N86:N89"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="M102:M105"/>
-    <mergeCell ref="M106:M109"/>
-    <mergeCell ref="M110:M113"/>
-    <mergeCell ref="N102:N105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="N106:N109"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="M122:M125"/>
-    <mergeCell ref="M134:M137"/>
-    <mergeCell ref="M146:M149"/>
-    <mergeCell ref="M158:M161"/>
-    <mergeCell ref="M170:M173"/>
-    <mergeCell ref="M182:M185"/>
-    <mergeCell ref="M194:M197"/>
-    <mergeCell ref="N110:N113"/>
-    <mergeCell ref="M114:M117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="M118:M121"/>
-    <mergeCell ref="N118:N121"/>
-    <mergeCell ref="N134:N137"/>
-    <mergeCell ref="M138:M141"/>
-    <mergeCell ref="N138:N141"/>
-    <mergeCell ref="M142:M145"/>
-    <mergeCell ref="N142:N145"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="M126:M129"/>
-    <mergeCell ref="N126:N129"/>
-    <mergeCell ref="M130:M133"/>
-    <mergeCell ref="N130:N133"/>
-    <mergeCell ref="N158:N161"/>
-    <mergeCell ref="M162:M165"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="N162:N165"/>
-    <mergeCell ref="M166:M169"/>
-    <mergeCell ref="N166:N169"/>
-    <mergeCell ref="N146:N149"/>
-    <mergeCell ref="M150:M153"/>
-    <mergeCell ref="N150:N153"/>
-    <mergeCell ref="M154:M157"/>
-    <mergeCell ref="N154:N157"/>
-    <mergeCell ref="N194:N197"/>
-    <mergeCell ref="N182:N185"/>
-    <mergeCell ref="M186:M189"/>
-    <mergeCell ref="N186:N189"/>
-    <mergeCell ref="M190:M193"/>
-    <mergeCell ref="N190:N193"/>
-    <mergeCell ref="N170:N173"/>
-    <mergeCell ref="M174:M177"/>
-    <mergeCell ref="N174:N177"/>
-    <mergeCell ref="M178:M181"/>
-    <mergeCell ref="N178:N181"/>
-    <mergeCell ref="A202:A205"/>
-    <mergeCell ref="B202:B205"/>
-    <mergeCell ref="M202:M205"/>
-    <mergeCell ref="N202:N205"/>
-    <mergeCell ref="A206:A209"/>
-    <mergeCell ref="B206:B209"/>
-    <mergeCell ref="M206:M209"/>
-    <mergeCell ref="N206:N209"/>
-    <mergeCell ref="M198:M201"/>
-    <mergeCell ref="N198:N201"/>
-    <mergeCell ref="P2:P5"/>
-    <mergeCell ref="P6:P9"/>
-    <mergeCell ref="P10:P13"/>
-    <mergeCell ref="P14:P17"/>
-    <mergeCell ref="P18:P21"/>
-    <mergeCell ref="P22:P25"/>
-    <mergeCell ref="P26:P29"/>
-    <mergeCell ref="P30:P33"/>
-    <mergeCell ref="P34:P37"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="P42:P45"/>
-    <mergeCell ref="P46:P49"/>
-    <mergeCell ref="P50:P53"/>
-    <mergeCell ref="P54:P57"/>
-    <mergeCell ref="P58:P61"/>
-    <mergeCell ref="P62:P65"/>
-    <mergeCell ref="P66:P69"/>
-    <mergeCell ref="P70:P73"/>
-    <mergeCell ref="P74:P77"/>
-    <mergeCell ref="P78:P81"/>
-    <mergeCell ref="P82:P85"/>
-    <mergeCell ref="P86:P89"/>
-    <mergeCell ref="P90:P93"/>
-    <mergeCell ref="P94:P97"/>
-    <mergeCell ref="P98:P101"/>
-    <mergeCell ref="P102:P105"/>
-    <mergeCell ref="P106:P109"/>
-    <mergeCell ref="P110:P113"/>
-    <mergeCell ref="P114:P117"/>
-    <mergeCell ref="P118:P121"/>
-    <mergeCell ref="P122:P125"/>
-    <mergeCell ref="P126:P129"/>
-    <mergeCell ref="P130:P133"/>
-    <mergeCell ref="P134:P137"/>
-    <mergeCell ref="P138:P141"/>
-    <mergeCell ref="P142:P145"/>
-    <mergeCell ref="P182:P185"/>
-    <mergeCell ref="P186:P189"/>
-    <mergeCell ref="P190:P193"/>
-    <mergeCell ref="P194:P197"/>
-    <mergeCell ref="P146:P149"/>
-    <mergeCell ref="P150:P153"/>
-    <mergeCell ref="P154:P157"/>
-    <mergeCell ref="P158:P161"/>
-    <mergeCell ref="P162:P165"/>
-    <mergeCell ref="P166:P169"/>
-    <mergeCell ref="P170:P173"/>
-    <mergeCell ref="P174:P177"/>
-    <mergeCell ref="P178:P181"/>
+    <mergeCell ref="O22:O25"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="M14:M17"/>
+    <mergeCell ref="O14:O17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="M18:M21"/>
+    <mergeCell ref="O18:O21"/>
+    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="M6:M9"/>
+    <mergeCell ref="O6:O9"/>
+    <mergeCell ref="M10:M13"/>
+    <mergeCell ref="O10:O13"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="N50:N53"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="M38:M41"/>
+    <mergeCell ref="N38:N41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="M42:M45"/>
+    <mergeCell ref="N42:N45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="M46:M49"/>
+    <mergeCell ref="N46:N49"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6904FD8-B353-43BA-98AA-BD92AF2D3F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F489A303-F557-4B2B-A107-156244108261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="2625" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2635,6 +2635,9 @@
       <c r="E114">
         <v>2024</v>
       </c>
+      <c r="F114">
+        <v>2026</v>
+      </c>
       <c r="M114" s="3">
         <v>9</v>
       </c>
@@ -2650,10 +2653,10 @@
         <v>12</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
@@ -2679,6 +2682,12 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117">
+        <v>9</v>
+      </c>
+      <c r="D117">
+        <v>9</v>
+      </c>
+      <c r="E117">
         <v>9</v>
       </c>
       <c r="M117" s="3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F489A303-F557-4B2B-A107-156244108261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5302A75D-6D38-4A5F-8A8F-B05A868938EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12225" yWindow="2625" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5302A75D-6D38-4A5F-8A8F-B05A868938EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8D52BE-34DD-4E4B-BA5D-0CBF8C29A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12225" yWindow="2625" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5910" yWindow="2265" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="160">
   <si>
     <t>第一季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -681,6 +681,10 @@
   </si>
   <si>
     <t>泡麵番，跟搖曳露營一樣棒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進擊的巨人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -738,11 +742,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3907,26 +3912,30 @@
       <c r="P197" s="3"/>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
+      <c r="A198" s="4">
+        <v>48</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
+      <c r="A199" s="4"/>
+      <c r="B199" s="4"/>
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
+      <c r="A200" s="4"/>
+      <c r="B200" s="4"/>
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
+      <c r="A201" s="4"/>
+      <c r="B201" s="4"/>
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
     </row>
@@ -3980,106 +3989,139 @@
     </row>
   </sheetData>
   <mergeCells count="257">
-    <mergeCell ref="P182:P185"/>
-    <mergeCell ref="P186:P189"/>
-    <mergeCell ref="P190:P193"/>
-    <mergeCell ref="P194:P197"/>
-    <mergeCell ref="P146:P149"/>
-    <mergeCell ref="P150:P153"/>
-    <mergeCell ref="P154:P157"/>
-    <mergeCell ref="P158:P161"/>
-    <mergeCell ref="P162:P165"/>
-    <mergeCell ref="P166:P169"/>
-    <mergeCell ref="P170:P173"/>
-    <mergeCell ref="P174:P177"/>
-    <mergeCell ref="P178:P181"/>
-    <mergeCell ref="P110:P113"/>
-    <mergeCell ref="P114:P117"/>
-    <mergeCell ref="P118:P121"/>
-    <mergeCell ref="P122:P125"/>
-    <mergeCell ref="P126:P129"/>
-    <mergeCell ref="P130:P133"/>
-    <mergeCell ref="P134:P137"/>
-    <mergeCell ref="P138:P141"/>
-    <mergeCell ref="P142:P145"/>
-    <mergeCell ref="P74:P77"/>
-    <mergeCell ref="P78:P81"/>
-    <mergeCell ref="P82:P85"/>
-    <mergeCell ref="P86:P89"/>
-    <mergeCell ref="P90:P93"/>
-    <mergeCell ref="P94:P97"/>
-    <mergeCell ref="P98:P101"/>
-    <mergeCell ref="P102:P105"/>
-    <mergeCell ref="P106:P109"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="P42:P45"/>
-    <mergeCell ref="P46:P49"/>
-    <mergeCell ref="P50:P53"/>
-    <mergeCell ref="P54:P57"/>
-    <mergeCell ref="P58:P61"/>
-    <mergeCell ref="P62:P65"/>
-    <mergeCell ref="P66:P69"/>
-    <mergeCell ref="P70:P73"/>
-    <mergeCell ref="P2:P5"/>
-    <mergeCell ref="P6:P9"/>
-    <mergeCell ref="P10:P13"/>
-    <mergeCell ref="P14:P17"/>
-    <mergeCell ref="P18:P21"/>
-    <mergeCell ref="P22:P25"/>
-    <mergeCell ref="P26:P29"/>
-    <mergeCell ref="P30:P33"/>
-    <mergeCell ref="P34:P37"/>
-    <mergeCell ref="A202:A205"/>
-    <mergeCell ref="B202:B205"/>
-    <mergeCell ref="M202:M205"/>
-    <mergeCell ref="N202:N205"/>
-    <mergeCell ref="A206:A209"/>
-    <mergeCell ref="B206:B209"/>
-    <mergeCell ref="M206:M209"/>
-    <mergeCell ref="N206:N209"/>
-    <mergeCell ref="M198:M201"/>
-    <mergeCell ref="N198:N201"/>
-    <mergeCell ref="N162:N165"/>
-    <mergeCell ref="M166:M169"/>
-    <mergeCell ref="N166:N169"/>
-    <mergeCell ref="N146:N149"/>
-    <mergeCell ref="M150:M153"/>
-    <mergeCell ref="N150:N153"/>
-    <mergeCell ref="M154:M157"/>
-    <mergeCell ref="N154:N157"/>
-    <mergeCell ref="N194:N197"/>
-    <mergeCell ref="N182:N185"/>
-    <mergeCell ref="M186:M189"/>
-    <mergeCell ref="N186:N189"/>
-    <mergeCell ref="M190:M193"/>
-    <mergeCell ref="N190:N193"/>
-    <mergeCell ref="N170:N173"/>
-    <mergeCell ref="M174:M177"/>
-    <mergeCell ref="N174:N177"/>
-    <mergeCell ref="M178:M181"/>
-    <mergeCell ref="N178:N181"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="N50:N53"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="M38:M41"/>
+    <mergeCell ref="N38:N41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="M42:M45"/>
+    <mergeCell ref="N42:N45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="M46:M49"/>
+    <mergeCell ref="N46:N49"/>
+    <mergeCell ref="O22:O25"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="M14:M17"/>
+    <mergeCell ref="O14:O17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="M18:M21"/>
+    <mergeCell ref="O18:O21"/>
+    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="M6:M9"/>
+    <mergeCell ref="O6:O9"/>
+    <mergeCell ref="M10:M13"/>
+    <mergeCell ref="O10:O13"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="N54:N57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="M58:M61"/>
+    <mergeCell ref="N58:N61"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="M22:M25"/>
+    <mergeCell ref="M30:M33"/>
+    <mergeCell ref="N30:N33"/>
+    <mergeCell ref="M26:M29"/>
+    <mergeCell ref="N26:N29"/>
+    <mergeCell ref="M34:M37"/>
+    <mergeCell ref="N34:N37"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="M50:M53"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="M54:M57"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="M90:M93"/>
+    <mergeCell ref="N90:N93"/>
+    <mergeCell ref="M94:M97"/>
+    <mergeCell ref="N94:N97"/>
+    <mergeCell ref="M98:M101"/>
+    <mergeCell ref="N98:N101"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="M62:M65"/>
+    <mergeCell ref="N62:N65"/>
+    <mergeCell ref="M66:M69"/>
+    <mergeCell ref="N66:N69"/>
+    <mergeCell ref="M70:M73"/>
+    <mergeCell ref="N70:N73"/>
+    <mergeCell ref="M74:M77"/>
+    <mergeCell ref="N74:N77"/>
+    <mergeCell ref="M78:M81"/>
+    <mergeCell ref="N78:N81"/>
+    <mergeCell ref="M82:M85"/>
+    <mergeCell ref="N82:N85"/>
+    <mergeCell ref="M86:M89"/>
+    <mergeCell ref="N86:N89"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="M102:M105"/>
+    <mergeCell ref="M106:M109"/>
+    <mergeCell ref="M110:M113"/>
+    <mergeCell ref="N102:N105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="N106:N109"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="B142:B145"/>
     <mergeCell ref="M122:M125"/>
     <mergeCell ref="M134:M137"/>
     <mergeCell ref="M146:M149"/>
@@ -4104,139 +4146,106 @@
     <mergeCell ref="N130:N133"/>
     <mergeCell ref="N158:N161"/>
     <mergeCell ref="M162:M165"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="M102:M105"/>
-    <mergeCell ref="M106:M109"/>
-    <mergeCell ref="M110:M113"/>
-    <mergeCell ref="N102:N105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="N106:N109"/>
-    <mergeCell ref="M90:M93"/>
-    <mergeCell ref="N90:N93"/>
-    <mergeCell ref="M94:M97"/>
-    <mergeCell ref="N94:N97"/>
-    <mergeCell ref="M98:M101"/>
-    <mergeCell ref="N98:N101"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="M62:M65"/>
-    <mergeCell ref="N62:N65"/>
-    <mergeCell ref="M66:M69"/>
-    <mergeCell ref="N66:N69"/>
-    <mergeCell ref="M70:M73"/>
-    <mergeCell ref="N70:N73"/>
-    <mergeCell ref="M74:M77"/>
-    <mergeCell ref="N74:N77"/>
-    <mergeCell ref="M78:M81"/>
-    <mergeCell ref="N78:N81"/>
-    <mergeCell ref="M82:M85"/>
-    <mergeCell ref="N82:N85"/>
-    <mergeCell ref="M86:M89"/>
-    <mergeCell ref="N86:N89"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="M54:M57"/>
-    <mergeCell ref="N54:N57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="M58:M61"/>
-    <mergeCell ref="N58:N61"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="M22:M25"/>
-    <mergeCell ref="M30:M33"/>
-    <mergeCell ref="N30:N33"/>
-    <mergeCell ref="M26:M29"/>
-    <mergeCell ref="N26:N29"/>
-    <mergeCell ref="M34:M37"/>
-    <mergeCell ref="N34:N37"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="M50:M53"/>
-    <mergeCell ref="O22:O25"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="M14:M17"/>
-    <mergeCell ref="O14:O17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="M18:M21"/>
-    <mergeCell ref="O18:O21"/>
-    <mergeCell ref="N2:N5"/>
-    <mergeCell ref="M6:M9"/>
-    <mergeCell ref="O6:O9"/>
-    <mergeCell ref="M10:M13"/>
-    <mergeCell ref="O10:O13"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="M2:M5"/>
-    <mergeCell ref="N50:N53"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="M38:M41"/>
-    <mergeCell ref="N38:N41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="M42:M45"/>
-    <mergeCell ref="N42:N45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="M46:M49"/>
-    <mergeCell ref="N46:N49"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="N162:N165"/>
+    <mergeCell ref="M166:M169"/>
+    <mergeCell ref="N166:N169"/>
+    <mergeCell ref="N146:N149"/>
+    <mergeCell ref="M150:M153"/>
+    <mergeCell ref="N150:N153"/>
+    <mergeCell ref="M154:M157"/>
+    <mergeCell ref="N154:N157"/>
+    <mergeCell ref="N194:N197"/>
+    <mergeCell ref="N182:N185"/>
+    <mergeCell ref="M186:M189"/>
+    <mergeCell ref="N186:N189"/>
+    <mergeCell ref="M190:M193"/>
+    <mergeCell ref="N190:N193"/>
+    <mergeCell ref="N170:N173"/>
+    <mergeCell ref="M174:M177"/>
+    <mergeCell ref="N174:N177"/>
+    <mergeCell ref="M178:M181"/>
+    <mergeCell ref="N178:N181"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="M202:M205"/>
+    <mergeCell ref="N202:N205"/>
+    <mergeCell ref="A206:A209"/>
+    <mergeCell ref="B206:B209"/>
+    <mergeCell ref="M206:M209"/>
+    <mergeCell ref="N206:N209"/>
+    <mergeCell ref="M198:M201"/>
+    <mergeCell ref="N198:N201"/>
+    <mergeCell ref="P2:P5"/>
+    <mergeCell ref="P6:P9"/>
+    <mergeCell ref="P10:P13"/>
+    <mergeCell ref="P14:P17"/>
+    <mergeCell ref="P18:P21"/>
+    <mergeCell ref="P22:P25"/>
+    <mergeCell ref="P26:P29"/>
+    <mergeCell ref="P30:P33"/>
+    <mergeCell ref="P34:P37"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="P42:P45"/>
+    <mergeCell ref="P46:P49"/>
+    <mergeCell ref="P50:P53"/>
+    <mergeCell ref="P54:P57"/>
+    <mergeCell ref="P58:P61"/>
+    <mergeCell ref="P62:P65"/>
+    <mergeCell ref="P66:P69"/>
+    <mergeCell ref="P70:P73"/>
+    <mergeCell ref="P74:P77"/>
+    <mergeCell ref="P78:P81"/>
+    <mergeCell ref="P82:P85"/>
+    <mergeCell ref="P86:P89"/>
+    <mergeCell ref="P90:P93"/>
+    <mergeCell ref="P94:P97"/>
+    <mergeCell ref="P98:P101"/>
+    <mergeCell ref="P102:P105"/>
+    <mergeCell ref="P106:P109"/>
+    <mergeCell ref="P110:P113"/>
+    <mergeCell ref="P114:P117"/>
+    <mergeCell ref="P118:P121"/>
+    <mergeCell ref="P122:P125"/>
+    <mergeCell ref="P126:P129"/>
+    <mergeCell ref="P130:P133"/>
+    <mergeCell ref="P134:P137"/>
+    <mergeCell ref="P138:P141"/>
+    <mergeCell ref="P142:P145"/>
+    <mergeCell ref="P182:P185"/>
+    <mergeCell ref="P186:P189"/>
+    <mergeCell ref="P190:P193"/>
+    <mergeCell ref="P194:P197"/>
+    <mergeCell ref="P146:P149"/>
+    <mergeCell ref="P150:P153"/>
+    <mergeCell ref="P154:P157"/>
+    <mergeCell ref="P158:P161"/>
+    <mergeCell ref="P162:P165"/>
+    <mergeCell ref="P166:P169"/>
+    <mergeCell ref="P170:P173"/>
+    <mergeCell ref="P174:P177"/>
+    <mergeCell ref="P178:P181"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8D52BE-34DD-4E4B-BA5D-0CBF8C29A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1930FF45-DAFD-4A37-814F-C13EB807317A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5910" yWindow="2265" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3940,25 +3940,27 @@
       <c r="N201" s="3"/>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A202" s="3"/>
+      <c r="A202" s="4">
+        <v>49</v>
+      </c>
       <c r="B202" s="3"/>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A203" s="3"/>
+      <c r="A203" s="4"/>
       <c r="B203" s="3"/>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A204" s="3"/>
+      <c r="A204" s="4"/>
       <c r="B204" s="3"/>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A205" s="3"/>
+      <c r="A205" s="4"/>
       <c r="B205" s="3"/>
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1930FF45-DAFD-4A37-814F-C13EB807317A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F7AAC3-D318-4B77-9ECC-871BE85B84FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5910" yWindow="2265" windowWidth="15795" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1245" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="163">
   <si>
     <t>第一季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -685,6 +685,17 @@
   </si>
   <si>
     <t>進擊的巨人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack on Titan.jpg</t>
+  </si>
+  <si>
+    <t>Re,Zero -Starting Life in Another World-.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Re:從零開始的異世界生活</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3918,50 +3929,123 @@
       <c r="B198" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="M198" s="3"/>
+      <c r="C198">
+        <v>2013</v>
+      </c>
+      <c r="D198">
+        <v>2017</v>
+      </c>
+      <c r="E198">
+        <v>2018</v>
+      </c>
+      <c r="F198">
+        <v>2020</v>
+      </c>
+      <c r="M198" s="4">
+        <v>9</v>
+      </c>
       <c r="N198" s="3"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
-      <c r="M199" s="3"/>
+      <c r="C199">
+        <v>25</v>
+      </c>
+      <c r="D199">
+        <v>12</v>
+      </c>
+      <c r="E199">
+        <v>22</v>
+      </c>
+      <c r="F199">
+        <v>35</v>
+      </c>
+      <c r="M199" s="4"/>
       <c r="N199" s="3"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
-      <c r="M200" s="3"/>
+      <c r="C200">
+        <v>25</v>
+      </c>
+      <c r="D200">
+        <v>12</v>
+      </c>
+      <c r="E200">
+        <v>22</v>
+      </c>
+      <c r="F200">
+        <v>35</v>
+      </c>
+      <c r="M200" s="4"/>
       <c r="N200" s="3"/>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
-      <c r="M201" s="3"/>
+      <c r="C201">
+        <v>9</v>
+      </c>
+      <c r="D201">
+        <v>9</v>
+      </c>
+      <c r="E201">
+        <v>9</v>
+      </c>
+      <c r="F201">
+        <v>9</v>
+      </c>
+      <c r="M201" s="4"/>
       <c r="N201" s="3"/>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>49</v>
       </c>
-      <c r="B202" s="3"/>
+      <c r="B202" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C202">
+        <v>2016</v>
+      </c>
+      <c r="D202">
+        <v>2020</v>
+      </c>
+      <c r="E202">
+        <v>2024</v>
+      </c>
+      <c r="F202">
+        <v>2026</v>
+      </c>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="4"/>
-      <c r="B203" s="3"/>
+      <c r="B203" s="4"/>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="3"/>
+      <c r="B204" s="4"/>
+      <c r="C204">
+        <v>25</v>
+      </c>
+      <c r="D204">
+        <v>25</v>
+      </c>
+      <c r="E204">
+        <v>16</v>
+      </c>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="4"/>
-      <c r="B205" s="3"/>
+      <c r="B205" s="4"/>
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
     </row>
@@ -4257,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B67153-A9B1-47E6-9F2F-F7B7EB14E9AD}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="77.28515625" customWidth="1"/>
@@ -4662,6 +4746,22 @@
         <v>123</v>
       </c>
     </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F7AAC3-D318-4B77-9ECC-871BE85B84FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBFC681-EC3B-4DB5-BEF7-48ED0C081966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2880" yWindow="1245" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3923,10 +3923,10 @@
       <c r="P197" s="3"/>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A198" s="4">
+      <c r="A198" s="3">
         <v>48</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C198">
@@ -3941,14 +3941,14 @@
       <c r="F198">
         <v>2020</v>
       </c>
-      <c r="M198" s="4">
+      <c r="M198" s="3">
         <v>9</v>
       </c>
       <c r="N198" s="3"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A199" s="4"/>
-      <c r="B199" s="4"/>
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
       <c r="C199">
         <v>25</v>
       </c>
@@ -3961,12 +3961,12 @@
       <c r="F199">
         <v>35</v>
       </c>
-      <c r="M199" s="4"/>
+      <c r="M199" s="3"/>
       <c r="N199" s="3"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A200" s="4"/>
-      <c r="B200" s="4"/>
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
       <c r="C200">
         <v>25</v>
       </c>
@@ -3979,12 +3979,12 @@
       <c r="F200">
         <v>35</v>
       </c>
-      <c r="M200" s="4"/>
+      <c r="M200" s="3"/>
       <c r="N200" s="3"/>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
       <c r="C201">
         <v>9</v>
       </c>
@@ -3997,14 +3997,14 @@
       <c r="F201">
         <v>9</v>
       </c>
-      <c r="M201" s="4"/>
+      <c r="M201" s="3"/>
       <c r="N201" s="3"/>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A202" s="4">
+      <c r="A202" s="3">
         <v>49</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C202">
@@ -4019,18 +4019,23 @@
       <c r="F202">
         <v>2026</v>
       </c>
-      <c r="M202" s="3"/>
+      <c r="M202" s="4">
+        <v>8</v>
+      </c>
       <c r="N202" s="3"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="4"/>
-      <c r="M203" s="3"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203">
+        <v>25</v>
+      </c>
+      <c r="M203" s="4"/>
       <c r="N203" s="3"/>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A204" s="4"/>
-      <c r="B204" s="4"/>
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
       <c r="C204">
         <v>25</v>
       </c>
@@ -4040,13 +4045,16 @@
       <c r="E204">
         <v>16</v>
       </c>
-      <c r="M204" s="3"/>
+      <c r="M204" s="4"/>
       <c r="N204" s="3"/>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A205" s="4"/>
-      <c r="B205" s="4"/>
-      <c r="M205" s="3"/>
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205">
+        <v>6</v>
+      </c>
+      <c r="M205" s="4"/>
       <c r="N205" s="3"/>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
@@ -4075,39 +4083,206 @@
     </row>
   </sheetData>
   <mergeCells count="257">
-    <mergeCell ref="N50:N53"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="M38:M41"/>
-    <mergeCell ref="N38:N41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="M42:M45"/>
-    <mergeCell ref="N42:N45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="M46:M49"/>
-    <mergeCell ref="N46:N49"/>
-    <mergeCell ref="O22:O25"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="M14:M17"/>
-    <mergeCell ref="O14:O17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="M18:M21"/>
-    <mergeCell ref="O18:O21"/>
-    <mergeCell ref="N2:N5"/>
-    <mergeCell ref="M6:M9"/>
-    <mergeCell ref="O6:O9"/>
-    <mergeCell ref="M10:M13"/>
-    <mergeCell ref="O10:O13"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="P182:P185"/>
+    <mergeCell ref="P186:P189"/>
+    <mergeCell ref="P190:P193"/>
+    <mergeCell ref="P194:P197"/>
+    <mergeCell ref="P146:P149"/>
+    <mergeCell ref="P150:P153"/>
+    <mergeCell ref="P154:P157"/>
+    <mergeCell ref="P158:P161"/>
+    <mergeCell ref="P162:P165"/>
+    <mergeCell ref="P166:P169"/>
+    <mergeCell ref="P170:P173"/>
+    <mergeCell ref="P174:P177"/>
+    <mergeCell ref="P178:P181"/>
+    <mergeCell ref="P110:P113"/>
+    <mergeCell ref="P114:P117"/>
+    <mergeCell ref="P118:P121"/>
+    <mergeCell ref="P122:P125"/>
+    <mergeCell ref="P126:P129"/>
+    <mergeCell ref="P130:P133"/>
+    <mergeCell ref="P134:P137"/>
+    <mergeCell ref="P138:P141"/>
+    <mergeCell ref="P142:P145"/>
+    <mergeCell ref="P74:P77"/>
+    <mergeCell ref="P78:P81"/>
+    <mergeCell ref="P82:P85"/>
+    <mergeCell ref="P86:P89"/>
+    <mergeCell ref="P90:P93"/>
+    <mergeCell ref="P94:P97"/>
+    <mergeCell ref="P98:P101"/>
+    <mergeCell ref="P102:P105"/>
+    <mergeCell ref="P106:P109"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="P42:P45"/>
+    <mergeCell ref="P46:P49"/>
+    <mergeCell ref="P50:P53"/>
+    <mergeCell ref="P54:P57"/>
+    <mergeCell ref="P58:P61"/>
+    <mergeCell ref="P62:P65"/>
+    <mergeCell ref="P66:P69"/>
+    <mergeCell ref="P70:P73"/>
+    <mergeCell ref="P2:P5"/>
+    <mergeCell ref="P6:P9"/>
+    <mergeCell ref="P10:P13"/>
+    <mergeCell ref="P14:P17"/>
+    <mergeCell ref="P18:P21"/>
+    <mergeCell ref="P22:P25"/>
+    <mergeCell ref="P26:P29"/>
+    <mergeCell ref="P30:P33"/>
+    <mergeCell ref="P34:P37"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="M202:M205"/>
+    <mergeCell ref="N202:N205"/>
+    <mergeCell ref="A206:A209"/>
+    <mergeCell ref="B206:B209"/>
+    <mergeCell ref="M206:M209"/>
+    <mergeCell ref="N206:N209"/>
+    <mergeCell ref="M198:M201"/>
+    <mergeCell ref="N198:N201"/>
+    <mergeCell ref="N162:N165"/>
+    <mergeCell ref="M166:M169"/>
+    <mergeCell ref="N166:N169"/>
+    <mergeCell ref="N146:N149"/>
+    <mergeCell ref="M150:M153"/>
+    <mergeCell ref="N150:N153"/>
+    <mergeCell ref="M154:M157"/>
+    <mergeCell ref="N154:N157"/>
+    <mergeCell ref="N194:N197"/>
+    <mergeCell ref="N182:N185"/>
+    <mergeCell ref="M186:M189"/>
+    <mergeCell ref="N186:N189"/>
+    <mergeCell ref="M190:M193"/>
+    <mergeCell ref="N190:N193"/>
+    <mergeCell ref="N170:N173"/>
+    <mergeCell ref="M174:M177"/>
+    <mergeCell ref="N174:N177"/>
+    <mergeCell ref="M178:M181"/>
+    <mergeCell ref="N178:N181"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="M122:M125"/>
+    <mergeCell ref="M134:M137"/>
+    <mergeCell ref="M146:M149"/>
+    <mergeCell ref="M158:M161"/>
+    <mergeCell ref="M170:M173"/>
+    <mergeCell ref="M182:M185"/>
+    <mergeCell ref="M194:M197"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="M114:M117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="M118:M121"/>
+    <mergeCell ref="N118:N121"/>
+    <mergeCell ref="N134:N137"/>
+    <mergeCell ref="M138:M141"/>
+    <mergeCell ref="N138:N141"/>
+    <mergeCell ref="M142:M145"/>
+    <mergeCell ref="N142:N145"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="M126:M129"/>
+    <mergeCell ref="N126:N129"/>
+    <mergeCell ref="M130:M133"/>
+    <mergeCell ref="N130:N133"/>
+    <mergeCell ref="N158:N161"/>
+    <mergeCell ref="M162:M165"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="M102:M105"/>
+    <mergeCell ref="M106:M109"/>
+    <mergeCell ref="M110:M113"/>
+    <mergeCell ref="N102:N105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="N106:N109"/>
+    <mergeCell ref="M90:M93"/>
+    <mergeCell ref="N90:N93"/>
+    <mergeCell ref="M94:M97"/>
+    <mergeCell ref="N94:N97"/>
+    <mergeCell ref="M98:M101"/>
+    <mergeCell ref="N98:N101"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="M62:M65"/>
+    <mergeCell ref="N62:N65"/>
+    <mergeCell ref="M66:M69"/>
+    <mergeCell ref="N66:N69"/>
+    <mergeCell ref="M70:M73"/>
+    <mergeCell ref="N70:N73"/>
+    <mergeCell ref="M74:M77"/>
+    <mergeCell ref="N74:N77"/>
+    <mergeCell ref="M78:M81"/>
+    <mergeCell ref="N78:N81"/>
+    <mergeCell ref="M82:M85"/>
+    <mergeCell ref="N82:N85"/>
+    <mergeCell ref="M86:M89"/>
+    <mergeCell ref="N86:N89"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="M54:M57"/>
     <mergeCell ref="N54:N57"/>
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="B58:B61"/>
@@ -4132,206 +4307,39 @@
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="M50:M53"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="M54:M57"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="M90:M93"/>
-    <mergeCell ref="N90:N93"/>
-    <mergeCell ref="M94:M97"/>
-    <mergeCell ref="N94:N97"/>
-    <mergeCell ref="M98:M101"/>
-    <mergeCell ref="N98:N101"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="M62:M65"/>
-    <mergeCell ref="N62:N65"/>
-    <mergeCell ref="M66:M69"/>
-    <mergeCell ref="N66:N69"/>
-    <mergeCell ref="M70:M73"/>
-    <mergeCell ref="N70:N73"/>
-    <mergeCell ref="M74:M77"/>
-    <mergeCell ref="N74:N77"/>
-    <mergeCell ref="M78:M81"/>
-    <mergeCell ref="N78:N81"/>
-    <mergeCell ref="M82:M85"/>
-    <mergeCell ref="N82:N85"/>
-    <mergeCell ref="M86:M89"/>
-    <mergeCell ref="N86:N89"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="M102:M105"/>
-    <mergeCell ref="M106:M109"/>
-    <mergeCell ref="M110:M113"/>
-    <mergeCell ref="N102:N105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="N106:N109"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="M122:M125"/>
-    <mergeCell ref="M134:M137"/>
-    <mergeCell ref="M146:M149"/>
-    <mergeCell ref="M158:M161"/>
-    <mergeCell ref="M170:M173"/>
-    <mergeCell ref="M182:M185"/>
-    <mergeCell ref="M194:M197"/>
-    <mergeCell ref="N110:N113"/>
-    <mergeCell ref="M114:M117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="M118:M121"/>
-    <mergeCell ref="N118:N121"/>
-    <mergeCell ref="N134:N137"/>
-    <mergeCell ref="M138:M141"/>
-    <mergeCell ref="N138:N141"/>
-    <mergeCell ref="M142:M145"/>
-    <mergeCell ref="N142:N145"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="M126:M129"/>
-    <mergeCell ref="N126:N129"/>
-    <mergeCell ref="M130:M133"/>
-    <mergeCell ref="N130:N133"/>
-    <mergeCell ref="N158:N161"/>
-    <mergeCell ref="M162:M165"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="N162:N165"/>
-    <mergeCell ref="M166:M169"/>
-    <mergeCell ref="N166:N169"/>
-    <mergeCell ref="N146:N149"/>
-    <mergeCell ref="M150:M153"/>
-    <mergeCell ref="N150:N153"/>
-    <mergeCell ref="M154:M157"/>
-    <mergeCell ref="N154:N157"/>
-    <mergeCell ref="N194:N197"/>
-    <mergeCell ref="N182:N185"/>
-    <mergeCell ref="M186:M189"/>
-    <mergeCell ref="N186:N189"/>
-    <mergeCell ref="M190:M193"/>
-    <mergeCell ref="N190:N193"/>
-    <mergeCell ref="N170:N173"/>
-    <mergeCell ref="M174:M177"/>
-    <mergeCell ref="N174:N177"/>
-    <mergeCell ref="M178:M181"/>
-    <mergeCell ref="N178:N181"/>
-    <mergeCell ref="A202:A205"/>
-    <mergeCell ref="B202:B205"/>
-    <mergeCell ref="M202:M205"/>
-    <mergeCell ref="N202:N205"/>
-    <mergeCell ref="A206:A209"/>
-    <mergeCell ref="B206:B209"/>
-    <mergeCell ref="M206:M209"/>
-    <mergeCell ref="N206:N209"/>
-    <mergeCell ref="M198:M201"/>
-    <mergeCell ref="N198:N201"/>
-    <mergeCell ref="P2:P5"/>
-    <mergeCell ref="P6:P9"/>
-    <mergeCell ref="P10:P13"/>
-    <mergeCell ref="P14:P17"/>
-    <mergeCell ref="P18:P21"/>
-    <mergeCell ref="P22:P25"/>
-    <mergeCell ref="P26:P29"/>
-    <mergeCell ref="P30:P33"/>
-    <mergeCell ref="P34:P37"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="P42:P45"/>
-    <mergeCell ref="P46:P49"/>
-    <mergeCell ref="P50:P53"/>
-    <mergeCell ref="P54:P57"/>
-    <mergeCell ref="P58:P61"/>
-    <mergeCell ref="P62:P65"/>
-    <mergeCell ref="P66:P69"/>
-    <mergeCell ref="P70:P73"/>
-    <mergeCell ref="P74:P77"/>
-    <mergeCell ref="P78:P81"/>
-    <mergeCell ref="P82:P85"/>
-    <mergeCell ref="P86:P89"/>
-    <mergeCell ref="P90:P93"/>
-    <mergeCell ref="P94:P97"/>
-    <mergeCell ref="P98:P101"/>
-    <mergeCell ref="P102:P105"/>
-    <mergeCell ref="P106:P109"/>
-    <mergeCell ref="P110:P113"/>
-    <mergeCell ref="P114:P117"/>
-    <mergeCell ref="P118:P121"/>
-    <mergeCell ref="P122:P125"/>
-    <mergeCell ref="P126:P129"/>
-    <mergeCell ref="P130:P133"/>
-    <mergeCell ref="P134:P137"/>
-    <mergeCell ref="P138:P141"/>
-    <mergeCell ref="P142:P145"/>
-    <mergeCell ref="P182:P185"/>
-    <mergeCell ref="P186:P189"/>
-    <mergeCell ref="P190:P193"/>
-    <mergeCell ref="P194:P197"/>
-    <mergeCell ref="P146:P149"/>
-    <mergeCell ref="P150:P153"/>
-    <mergeCell ref="P154:P157"/>
-    <mergeCell ref="P158:P161"/>
-    <mergeCell ref="P162:P165"/>
-    <mergeCell ref="P166:P169"/>
-    <mergeCell ref="P170:P173"/>
-    <mergeCell ref="P174:P177"/>
-    <mergeCell ref="P178:P181"/>
+    <mergeCell ref="O22:O25"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="M14:M17"/>
+    <mergeCell ref="O14:O17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="M18:M21"/>
+    <mergeCell ref="O18:O21"/>
+    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="M6:M9"/>
+    <mergeCell ref="O6:O9"/>
+    <mergeCell ref="M10:M13"/>
+    <mergeCell ref="O10:O13"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="N50:N53"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="M38:M41"/>
+    <mergeCell ref="N38:N41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="M42:M45"/>
+    <mergeCell ref="N42:N45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="M46:M49"/>
+    <mergeCell ref="N46:N49"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBFC681-EC3B-4DB5-BEF7-48ED0C081966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A006295C-0FE5-4FD8-B725-B575FE3CDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2880" yWindow="1245" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4030,6 +4030,12 @@
       <c r="C203">
         <v>25</v>
       </c>
+      <c r="D203">
+        <v>25</v>
+      </c>
+      <c r="E203">
+        <v>16</v>
+      </c>
       <c r="M203" s="4"/>
       <c r="N203" s="3"/>
     </row>
@@ -4053,6 +4059,12 @@
       <c r="B205" s="3"/>
       <c r="C205">
         <v>6</v>
+      </c>
+      <c r="D205">
+        <v>8</v>
+      </c>
+      <c r="E205">
+        <v>8</v>
       </c>
       <c r="M205" s="4"/>
       <c r="N205" s="3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A006295C-0FE5-4FD8-B725-B575FE3CDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43174A2D-6B9C-47CA-B411-4F37AEDDF463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1245" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12870" yWindow="2775" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="165">
   <si>
     <t>第一季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -696,6 +696,14 @@
   </si>
   <si>
     <t>Re:從零開始的異世界生活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>憂國的莫里亞蒂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Moriarty the Patriot.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4070,26 +4078,42 @@
       <c r="N205" s="3"/>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A206" s="3"/>
-      <c r="B206" s="3"/>
+      <c r="A206" s="4">
+        <v>50</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C206">
+        <v>2020</v>
+      </c>
+      <c r="D206">
+        <v>2021</v>
+      </c>
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A207" s="3"/>
-      <c r="B207" s="3"/>
+      <c r="A207" s="4"/>
+      <c r="B207" s="4"/>
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A208" s="3"/>
-      <c r="B208" s="3"/>
+      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
+      <c r="C208">
+        <v>11</v>
+      </c>
+      <c r="D208">
+        <v>13</v>
+      </c>
       <c r="M208" s="3"/>
       <c r="N208" s="3"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" s="3"/>
-      <c r="B209" s="3"/>
+      <c r="A209" s="4"/>
+      <c r="B209" s="4"/>
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
     </row>
@@ -4361,7 +4385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B67153-A9B1-47E6-9F2F-F7B7EB14E9AD}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="77.28515625" customWidth="1"/>
@@ -4782,6 +4806,14 @@
         <v>161</v>
       </c>
     </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43174A2D-6B9C-47CA-B411-4F37AEDDF463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FF8FE8-AFCD-4D7F-A4EB-F7120C71AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="2775" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14850" yWindow="3150" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3689,7 +3689,7 @@
         <v>2019</v>
       </c>
       <c r="M178" s="3">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N178" s="3"/>
       <c r="P178" s="3"/>
@@ -3718,7 +3718,7 @@
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
@@ -4028,7 +4028,7 @@
         <v>2026</v>
       </c>
       <c r="M202" s="4">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N202" s="3"/>
     </row>
@@ -4069,10 +4069,10 @@
         <v>6</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E205">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M205" s="4"/>
       <c r="N205" s="3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FF8FE8-AFCD-4D7F-A4EB-F7120C71AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C0F36-25EE-4E38-9D49-FB51E2B431E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14850" yWindow="3150" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4028,7 +4028,7 @@
         <v>2026</v>
       </c>
       <c r="M202" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N202" s="3"/>
     </row>
@@ -4069,10 +4069,10 @@
         <v>6</v>
       </c>
       <c r="D205">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E205">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="M205" s="4"/>
       <c r="N205" s="3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C0F36-25EE-4E38-9D49-FB51E2B431E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F720587-4256-4D24-9A62-9B5A26469A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14850" yWindow="3150" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8385" yWindow="3150" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="166">
   <si>
     <t>第一季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -704,6 +704,10 @@
   </si>
   <si>
     <t>Moriarty the Patriot.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BanG Dream! Ave Mujica.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4090,13 +4094,21 @@
       <c r="D206">
         <v>2021</v>
       </c>
-      <c r="M206" s="3"/>
+      <c r="M206" s="4">
+        <v>7.5</v>
+      </c>
       <c r="N206" s="3"/>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
-      <c r="M207" s="3"/>
+      <c r="C207">
+        <v>11</v>
+      </c>
+      <c r="D207">
+        <v>13</v>
+      </c>
+      <c r="M207" s="4"/>
       <c r="N207" s="3"/>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
@@ -4108,13 +4120,19 @@
       <c r="D208">
         <v>13</v>
       </c>
-      <c r="M208" s="3"/>
+      <c r="M208" s="4"/>
       <c r="N208" s="3"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
-      <c r="M209" s="3"/>
+      <c r="C209">
+        <v>7.5</v>
+      </c>
+      <c r="D209">
+        <v>8</v>
+      </c>
+      <c r="M209" s="4"/>
       <c r="N209" s="3"/>
     </row>
   </sheetData>
@@ -4385,7 +4403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B67153-A9B1-47E6-9F2F-F7B7EB14E9AD}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="77.28515625" customWidth="1"/>
@@ -4814,6 +4832,14 @@
         <v>164</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data_anime.xlsx
+++ b/database/data_anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\githubpage\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F720587-4256-4D24-9A62-9B5A26469A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D467D23B-890B-4AC1-BA6F-E40C13F61699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8385" yWindow="3150" windowWidth="17460" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3589,10 +3589,10 @@
         <v>12</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
@@ -3630,6 +3630,12 @@
         <v>10</v>
       </c>
       <c r="E173">
+        <v>10</v>
+      </c>
+      <c r="F173">
+        <v>10</v>
+      </c>
+      <c r="G173">
         <v>10</v>
       </c>
       <c r="M173" s="3"/>
